--- a/docs/v0.3/04_test_cases_manual_v03.xlsx
+++ b/docs/v0.3/04_test_cases_manual_v03.xlsx
@@ -15,6 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_세율표" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_장특공표" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_중과판정" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_TC-S01" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_TC-S02" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_TC-S03" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_TC-S04" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_시나리오비교" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_상태전이흐름도" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,8 +29,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -63,7 +70,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +105,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFD966"/>
         <bgColor rgb="00FFD966"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+        <bgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -171,7 +190,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,6 +243,45 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1023,6 +1081,2687 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D71"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC-S02 — 2주택자 2채 양도 (TYPE_2_ORDER) — 상태전이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>입력 (A·B 동일 자산, saleRegulated만 다름)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>필드 (한글 명칭 / 변수명)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도가액·취득가액·필요경비</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>10억 / 5억 / 2천만</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>A·B 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 보유연수</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>12년</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2014-05-01 ~ 2026-09-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-A 핵심</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>★ 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도가액·취득가액·필요경비</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>10억 / 5억 / 2천만</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>A·B 동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 보유연수</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>12년</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>동일</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-A 핵심</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>★ 비조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 양도할 주택수 (targetSaleCount)</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-B 시나리오</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>모두 양도</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 후보 주택 (candidateHouseIds)</t>
+        </is>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>[A, B]</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-B 시나리오</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>핵심 메시지 — 상태전이가 결과를 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>▪ A·B 모든 입력이 동일 (saleRegulated만 다름). 양도 순서가 totalTax 합계를 결정적으로 분기.</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>▪ SC-1 (A→B): A 먼저 양도 → +20%p 중과. B 2번째 양도 → 1주택 + 비과세 미적용.</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>▪ SC-2 (B→A): B 먼저 양도 → 비조정대상 → 중과 미발동. A 2번째 양도 → 1주택 + 비과세 미적용.</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="6" t="n"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SC-1 양도 1번째 (A 양도, householdHouseCount=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>변수 (한글 / 영문)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>양도 전</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>기본공제 사용 (basicDeductionUsed)</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>★ 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>4조건 충족</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>가산세율 (heavyRateAddition)</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 — A (totalTax_A)</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>286616000</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>★ TC-011 정답값</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SC-1 양도 2번째 (B 양도, householdHouseCount=1 — 상태전이)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>★ 상태전이: 2 → 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>기본공제 사용 (basicDeductionUsed)</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>★ 동일 연도 + 1번째에서 사용</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>1세대1주택 비과세 (is1Se1House)</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>거주 0M → 거주요건 미충족</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>조건 1 미충족 (1주택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>장특공 표 (appliedDeductionTable)</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>1주택 + 비과세 미적용 → 표 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>보유연수 (holdingYears)</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>장기보유특별공제 (longTermDeduction)</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="n">
+        <v>115200000</v>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>floor(480,000,000 × 0.24)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>과세표준 (taxBase)</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="n">
+        <v>364800000</v>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>480,000,000 − 115,200,000 − 0 (기본공제 0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 — B (totalTax_B)</t>
+        </is>
+      </c>
+      <c r="C39" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>★ 검증팀 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="22" customHeight="1">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SC-1 합계</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Σ totalTax (총 납부세액 합계)</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>286,616,000 + ⏳ = ⏳</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Σ netAfterTaxSaleAmount (세후 매각금액 합계)</t>
+        </is>
+      </c>
+      <c r="B43" s="29" t="inlineStr">
+        <is>
+          <t>(1,000,000,000 − 286,616,000) + (1,000,000,000 − ⏳) = ⏳</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n"/>
+      <c r="D43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate, 평균)</t>
+        </is>
+      </c>
+      <c r="B44" s="29" t="inlineStr">
+        <is>
+          <t>Σ totalTax / 2,000,000,000 = ⏳</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n"/>
+      <c r="D44" s="6" t="n"/>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>SC-2 양도 1번째 (B 양도, householdHouseCount=2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>조건 2 미충족 (비조정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>장특공 표 (appliedDeductionTable)</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>다주택 + 표 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>장기보유특별공제 (longTermDeduction)</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="n">
+        <v>115200000</v>
+      </c>
+      <c r="D50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>과세표준 (taxBase)</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="n">
+        <v>362300000</v>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>480,000,000 − 115,200,000 − 2,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 — B (totalTax_B)</t>
+        </is>
+      </c>
+      <c r="C52" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>TC-008 유사 패턴 (검증)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>SC-2 양도 2번째 (A 양도, householdHouseCount=1 — 상태전이)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>★ 상태전이: 2 → 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>기본공제 사용 (basicDeductionUsed)</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>★ 동일 연도</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>조건 1 미충족 (1주택)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 — A (totalTax_A)</t>
+        </is>
+      </c>
+      <c r="C59" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>검증팀 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>비교 정렬 (D안 — TYPE_2_ORDER → Σ netAfterTaxSaleAmount desc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="10" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Σ totalTax (예상)</t>
+        </is>
+      </c>
+      <c r="C62" s="10" t="inlineStr">
+        <is>
+          <t>Σ netAfterTaxSaleAmount (예상)</t>
+        </is>
+      </c>
+      <c r="D62" s="10" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>SC-1 (A→B)</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>큼 (1번째 +20%p 중과)</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>작음</t>
+        </is>
+      </c>
+      <c r="D63" s="23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>SC-2 (B→A)</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>작음 (양쪽 중과 미발동)</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>큼 (★ 우수)</t>
+        </is>
+      </c>
+      <c r="D64" s="23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>검증 의도 — TYPE_2_ORDER 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>▪ A·B 동일 자산이지만 saleRegulated 1개만 다름.</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n"/>
+      <c r="C67" s="5" t="n"/>
+      <c r="D67" s="6" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>▪ A 먼저 양도(SC-1) → 1번째에서 +20%p 중과 부담. B 먼저 양도(SC-2) → 양쪽 양도 모두 중과 미발동.</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="n"/>
+      <c r="C68" s="5" t="n"/>
+      <c r="D68" s="6" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>▪ 의사결정 #10 D안의 '양도 순서 비교' 정확 작동 검증.</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="n"/>
+      <c r="C69" s="5" t="n"/>
+      <c r="D69" s="6" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>▪ Σ netAfterTaxSaleAmount 합계로 정렬 시 SC-2가 우수해야 함.</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="n"/>
+      <c r="C70" s="5" t="n"/>
+      <c r="D70" s="6" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>▪ 상태전이 메커니즘: 양도 1번째 후 householdHouseCount 감소 + 동일 연도 시 basicDeductionUsed=true.</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="B43:D43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC-S03 — 3주택자 1채 양도 (TYPE_1_WHICH_ONE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>입력 — 3주택자 (A·B 조정대상 / C 비조정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>필드 (한글 / 영문)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>3주택</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도가액 (expectedSalePrice)</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>10억</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도가액 (expectedSalePrice)</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>9억</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>주택 C — 양도가액 (expectedSalePrice)</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>8억</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>주택 C — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>★ 비조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 양도할 주택수 (targetSaleCount)</t>
+        </is>
+      </c>
+      <c r="B12" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>1채만</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>시나리오 — SC-1·SC-2·SC-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>양도 주택</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>다주택 중과</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>기대 totalTax</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>SC-1</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>A 양도 (10억, 조정)</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>발동 +30%p</t>
+        </is>
+      </c>
+      <c r="D16" s="29" t="inlineStr">
+        <is>
+          <t>TC-012 패턴 (검증 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>SC-2</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>B 양도 (9억, 조정)</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>발동 +30%p</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="inlineStr">
+        <is>
+          <t>(9억 + 동일 산식, 검증 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>SC-3</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>C 양도 (8억, 비조정)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>미발동</t>
+        </is>
+      </c>
+      <c r="D18" s="29" t="inlineStr">
+        <is>
+          <t>(다주택 일반과세, 검증 대기)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>비교 정렬 (D안 — TYPE_1_WHICH_ONE → effectiveTaxRate asc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate, 예상)</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>SC-1 (A 양도)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>매우 높음 (+30%p)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>SC-2 (B 양도)</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>매우 높음 (+30%p)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>SC-3 (C 양도, 비조정)</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>낮음 (중과 없음)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1 (★)</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>★ 우수</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>검증 의도</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>▪ 3주택 + 첫 양도 시 +30%p 중과 (TC-012 패턴).</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>▪ 비조정대상 주택(C)을 양도하면 중과 미발동 → effectiveTaxRate 크게 낮음.</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>▪ TYPE_1_WHICH_ONE의 D안 1순위 지표(effectiveTaxRate) 정상 작동 검증.</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>▪ 검증팀 손계산 + 홈택스 모의계산 (양도 1건씩, 3건).</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A14:D14"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC-S04 (선택) — 2주택자 2채 시점 분산 (TYPE_3_TIMING)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>입력 — 2주택자 + 시점 분산 허용</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>필드 (한글 / 영문)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>highlight</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>비조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 양도할 주택수 (targetSaleCount)</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>모두 양도</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 시점 분산 허용 (allowYearSplitting)</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>★ 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 후보 연도 (targetSaleYears)</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>[2026, 2027]</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>★ 2개 연도</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>시나리오 — 단조 비감소 시점 적용 (6개 시나리오)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>양도 순서 (ordered)</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>양도 연도 (years)</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>기대 효과</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>SC-1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>[A, B]</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>[2026, 2026]</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>동일 연도, 기본공제 250만원 1번</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>SC-2</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>[A, B]</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>[2026, 2027]</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>분산, 기본공제 × 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>SC-3</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>[A, B]</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>[2027, 2027]</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>동일 연도 (2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>SC-4</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>[B, A]</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>[2026, 2026]</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>B→A 순서</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>SC-5</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>[B, A]</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>[2026, 2027]</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>B→A, 분산</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>SC-6</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>[B, A]</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>[2027, 2027]</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>B→A, 동일 연도 (2027)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>비교 정렬 (D안 — TYPE_3_TIMING → Σ netAfterTaxSaleAmount desc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>▪ hasTimingSpread = TRUE → 우선순위 1 → TYPE_3_TIMING</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>▪ metricKey = netAfterTaxSaleAmount, order = desc</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="6" t="n"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>정답값 — 검증팀 결정 권고 (선택 케이스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>▪ 6개 시나리오의 정확한 totalTax 산출은 검증팀 손계산 + 홈택스 모의계산.</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>▪ 본 명세서는 산식 흐름과 기대 시나리오 타입만 명시.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>▪ 본질 가치 4영역 NPV 미통합 상태에서 시점 분산은 기본공제 250만원 효과만 검증 가능 (제한적).</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>▪ post-MVP B-030 (통합 NPV) 통합 후 본격 검증 권고.</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>시나리오 비교 정렬 — 의사결정 #10 D안 + 보강 4건</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. D안 정렬 지표 — 시나리오 타입별 metricKey</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>시나리오 타입</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>metricKey (정렬 지표)</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>order (정렬 순서)</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>TYPE_1_WHICH_ONE
+(어느 1채 양도?)</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>asc (낮을수록 우수)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>양도가액 종속 회피</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>TYPE_2_ORDER
+(같은 자산, 다른 순서)</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Σ 세후 매각금액 (netAfterTaxSaleAmount)</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>desc (클수록 우수)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>절대값 비교 가능</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>TYPE_3_TIMING
+(같은 자산·순서, 다른 시점)</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Σ 세후 매각금액 (netAfterTaxSaleAmount)</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>시점 차이를 절대값으로</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2. tiebreaker 4단계 — 동률 처리</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>우선순위</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>tiebreaker 지표</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>주 metricKey</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>TYPE별 D안 지표</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Σ totalTax (총 납부세액 합계)</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>낮을수록 우수</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>양도 시점 (referenceYear)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>이른 시점 우선</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>시나리오 ID (scenario_id)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>사전순</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>3. 보강 4건 (의사결정 #10 정본)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>보강 내용</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>함수 / 필드</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>보강 1</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>metricKey 인자화</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>sortScenariosByMetric(scenarios, metricKey)</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>시나리오 엔진이 metricKey 받음</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>보강 2</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>시나리오 타입 분류 함수</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>classifyScenarioDimensions·selectMetricKey</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>차원 태그 기반</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>보강 3</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>결과 객체 표준화</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>result.scenarios (배열)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>rank·metric_value·actions[] 포함</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>보강 4</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>미정·정해짐 시나리오 분기</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>salePlan.allowSystemToChooseSaleTargets</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>true/false 분기</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A16:D16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>상태전이 흐름도 — 양도 순서 + 잔여 주택수 변동</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. 상태전이 메커니즘</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>처리</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>변화 변수</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>단계 1</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>양도 1번째 (예: A)</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>calculateSingleTransfer(A)</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>totalTax_A 산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>단계 2</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>잔여 주택수 변동</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>householdHouseCount: N → N−1</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>★ 상태전이 핵심</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="inlineStr">
+        <is>
+          <t>단계 3</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>기본공제 사용 여부</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>basicDeductionUsed: false → true (동일 연도)</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>기본공제 250만원 1번만</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>단계 4</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>양도 2번째 (예: B)</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>calculateSingleTransfer(B, 변동된 caseData)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>totalTax_B 산출</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>단계 5</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>합계 산출</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Σ totalTax + Σ netAfterTaxSaleAmount</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>시나리오 결과</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2. 다주택 중과 분기 변경 — 양도 순서 차이</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>케이스</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>양도 1번째</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>양도 2번째</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>totalTax 합계 영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="inlineStr">
+        <is>
+          <t>3주택자 (모두 양도 가정)</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>3주택 중과 +30%p</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>2주택 중과 +20%p</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>양도 순서가 양쪽 분기 모두 영향</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>2주택자 (모두 양도)</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>2주택 중과 +20%p (조정)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>1주택 비과세 가능</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>양도 순서가 비과세 적용 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>2주택자 (A 조정 / B 비조정)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>조정 → +20%p / 비조정 → 0</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1주택 + 비과세 미적용</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>★ TC-S02 핵심 케이스</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>3. 상태전이 핵심 변수 (한글 명칭 / 영문 변수명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>변수 (한글)</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>변수 (영문)</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>1번째 → 2번째 변동</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>householdHouseCount</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>N → N−1</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 조건 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>기본공제 사용 여부</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>basicDeductionUsed</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>false → true (동일 연도)</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>양도소득 기본공제 250만원</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>양도시 조정대상</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>saleRegulated</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>주택별 다름</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 조건 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>1세대1주택 비과세</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>is1Se1House</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>다주택 → 1주택 가능</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>거주요건 검증 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>isHeavyTaxation</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>조건 1·2·3·4 AND</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>양도 순서가 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>4. 상태전이 검증 영역 (TC-S02·TC-S04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>▪ TC-S02: 2주택 양도 순서 (A→B vs B→A) — 양도 순서가 totalTax 합계 결정.</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>▪ TC-S04 (선택): 시점 분산 (동일 연도 vs 분산) — 기본공제 250만원 효과 검증.</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>▪ 본질 가치 4영역 NPV (B-030, post-MVP) 통합 시 시점 분산의 본질 가치 명확화.</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A28:D28"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -5440,4 +8179,1212 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TC-S01 — 2주택자 1채 양도 (TYPE_1_WHICH_ONE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>입력 (caseData)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>필드 (한글 명칭 / 변수명)</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>기준연도 (baseYear)</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>세대원수 (householdMembers)</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>기본공제 사용여부 (basicDeductionUsed)</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>세대 보유 주택수 (householdHouseCount)</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>2주택</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>일시적 2주택 여부 (isOneTimeTwoHouses)</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 식별자 (id)</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 취득일 (acquisitionDate)</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>2014-05-01</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 취득가액 (acquisitionPrice)</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>5억</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 필요경비 (necessaryExpense)</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 취득시 조정대상 (acquisitionRegulated)</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 거주개월수 (residenceMonths)</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>거주 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도예정일 (expectedSaleDate)</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도예정가액 (expectedSalePrice)</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="n">
+        <v>1000000000</v>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>10억</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>주택 A — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-A 핵심</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>★ 중과 발동</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 식별자 (id)</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 취득일 (acquisitionDate)</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>2018-03-10</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 취득가액 (acquisitionPrice)</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="n">
+        <v>600000000</v>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>6억</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 필요경비 (necessaryExpense)</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 거주개월수 (residenceMonths)</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도예정일 (expectedSaleDate)</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도예정가액 (expectedSalePrice)</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="n">
+        <v>900000000</v>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>9억</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>주택 B — 양도시 조정대상 (saleRegulated)</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-A 핵심</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>★ 비조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 양도할 주택수 (targetSaleCount)</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-B 시나리오</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>1채만</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>양도 계획 — 후보 주택 (candidateHouseIds)</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>[A, B]</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>v0.3-B 시나리오</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>어느 1채?</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>시나리오 생성 흐름 (v0.3-B 신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>함수 (한글 명칭 / 변수명)</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>결과</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>타입</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>시나리오 차원 분류 (classifyScenarioDimensions)</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>{후보다수: TRUE, 순서결정: FALSE, 시점분산: FALSE}</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>정렬지표 결정 (selectMetricKey)</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>{타입: TYPE_1_WHICH_ONE, 지표: effectiveTaxRate, 정렬: asc}</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>object</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>양도가액 종속 회피</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>매도 대상 조합 (generateSaleTargetCombinations)</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>[{A}, {B}]</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>2개 조합</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>양도 순서 (generateSaleOrderScenarios)</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>[[A], [B]]</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>2개 (자명)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>양도 연도 (generateSaleYearScenarios)</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>[{ordered:[A], years:[2026]}, {ordered:[B], years:[2026]}]</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>array</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>2개</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SC-1 시뮬레이션 — A 양도 (TC-011 케이스 동일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>변수 (한글 / 영문)</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>산식 / 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>양도차익 (transferGain)</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="n">
+        <v>480000000</v>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>1,000,000,000 − 500,000,000 − 20,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>4단계 조건 모두 충족</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>가산세율 (heavyRateAddition)</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>2주택</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>장기보유특별공제 (longTermDeduction)</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>중과 시 배제</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>과세표준 (taxBase)</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="n">
+        <v>477500000</v>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>480,000,000 − 2,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>산출세액 (calculatedTax)</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>260560000</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>TC-011 산식</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>지방소득세 (localIncomeTax)</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="n">
+        <v>26056000</v>
+      </c>
+      <c r="D46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 (totalTax)</t>
+        </is>
+      </c>
+      <c r="C47" s="27" t="n">
+        <v>286616000</v>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>★ TC-011 정답값</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>세후 매각금액 (netAfterTaxSaleAmount)</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="n">
+        <v>713384000</v>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>1,000,000,000 − 286,616,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate)</t>
+        </is>
+      </c>
+      <c r="C49" s="28" t="n">
+        <v>0.286616</v>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>286,616,000 / 1,000,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>SC-2 시뮬레이션 — B 양도 (검증팀 손계산 영역)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>단계</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>변수 (한글 / 영문)</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>값</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>산식 / 비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>양도차익 (transferGain)</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="n">
+        <v>285000000</v>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>900,000,000 − 600,000,000 − 15,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>다주택 중과 발동 (isHeavyTaxation)</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>조건 2 미충족 (saleRegulated=false)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>장특공 표 (appliedDeductionTable)</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>다주택 + 표 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>보유연수 (holdingYears)</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>2018-03 → 2026-09 (8년 6개월)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>장기보유특별공제 (longTermDeduction)</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="n">
+        <v>45600000</v>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>floor(285,000,000 × 0.16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>양도소득금액 (capitalGainIncome)</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="n">
+        <v>239400000</v>
+      </c>
+      <c r="D58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>과세표준 (taxBase)</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="n">
+        <v>236900000</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>239,400,000 − 2,500,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>산출세액 (calculatedTax)</t>
+        </is>
+      </c>
+      <c r="C60" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>검증팀 검증 대기 (참고: 56,773,000 또는 57,118,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>지방소득세 (localIncomeTax)</t>
+        </is>
+      </c>
+      <c r="C61" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>검증팀</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>총 납부세액 (totalTax)</t>
+        </is>
+      </c>
+      <c r="C62" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>★ 검증팀 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate)</t>
+        </is>
+      </c>
+      <c r="C63" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>totalTax / 900,000,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>비교 정렬 (D안 정렬 지표 — TYPE_1_WHICH_ONE → effectiveTaxRate asc)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>시나리오</t>
+        </is>
+      </c>
+      <c r="B66" s="10" t="inlineStr">
+        <is>
+          <t>실효세율 (effectiveTaxRate)</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="D66" s="10" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>SC-1 (A 양도)</t>
+        </is>
+      </c>
+      <c r="B67" s="30" t="n">
+        <v>0.286616</v>
+      </c>
+      <c r="C67" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>+20%p 중과 → 실효세율 큼</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>SC-2 (B 양도)</t>
+        </is>
+      </c>
+      <c r="B68" s="29" t="inlineStr">
+        <is>
+          <t>⏳</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>1 (예상)</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>비조정대상 → 실효세율 작음 (낮을수록 우수)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>검증 의도</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>▪ TYPE_1_WHICH_ONE의 핵심 검증: 양도가액 종속 회피를 위해 effectiveTaxRate 1순위 정렬.</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="n"/>
+      <c r="C71" s="5" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>▪ A의 totalTax(286,616,000)가 B보다 클 가능성 큼. 다만 양도가액(10억 vs 9억)이 다르므로 절대값 비교 불가.</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="n"/>
+      <c r="C72" s="5" t="n"/>
+      <c r="D72" s="6" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>▪ effectiveTaxRate로 비교하면 A는 28.66%, B는 (검증 대기). B가 비조정대상이라 중과 미발동 → effectiveTaxRate 작음 → SC-2가 우수.</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="n"/>
+      <c r="C73" s="5" t="n"/>
+      <c r="D73" s="6" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>▪ 검증팀 손계산 + 홈택스 모의계산 (B 양도 단독으로 모의계산 가능).</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n"/>
+      <c r="D74" s="6" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A51:D51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>